--- a/analytikI/vystup.xlsx
+++ b/analytikI/vystup.xlsx
@@ -7,8 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Osoby" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Firmy" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Platy" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -18,17 +17,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="3">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
-      <color rgb="0000FF00"/>
     </font>
     <font>
       <b val="1"/>
@@ -58,7 +53,7 @@
   <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="4" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -133,6 +128,145 @@
     </indexedColors>
   </colors>
 </styleSheet>
+</file>
+
+<file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
+<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+  <chart>
+    <title>
+      <tx>
+        <rich>
+          <a:bodyPr/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr/>
+            </a:pPr>
+            <a:r>
+              <a:t>Platy zamestnancov</a:t>
+            </a:r>
+          </a:p>
+        </rich>
+      </tx>
+    </title>
+    <plotArea>
+      <barChart>
+        <barDir val="col"/>
+        <grouping val="clustered"/>
+        <ser>
+          <idx val="0"/>
+          <order val="0"/>
+          <tx>
+            <strRef>
+              <f>'Platy'!C2</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <cat>
+            <numRef>
+              <f>'Platy'!$B$2:$B$6</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Platy'!$C$3:$C$6</f>
+            </numRef>
+          </val>
+        </ser>
+        <gapWidth val="150"/>
+        <axId val="10"/>
+        <axId val="100"/>
+      </barChart>
+      <catAx>
+        <axId val="10"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <axPos val="l"/>
+        <title>
+          <tx>
+            <rich>
+              <a:bodyPr/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr/>
+                </a:pPr>
+                <a:r>
+                  <a:t>Meno</a:t>
+                </a:r>
+              </a:p>
+            </rich>
+          </tx>
+        </title>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="100"/>
+        <lblOffset val="100"/>
+      </catAx>
+      <valAx>
+        <axId val="100"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <axPos val="l"/>
+        <majorGridlines/>
+        <title>
+          <tx>
+            <rich>
+              <a:bodyPr/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr/>
+                </a:pPr>
+                <a:r>
+                  <a:t>€</a:t>
+                </a:r>
+              </a:p>
+            </rich>
+          </tx>
+        </title>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="10"/>
+      </valAx>
+    </plotArea>
+    <legend>
+      <legendPos val="r"/>
+    </legend>
+    <plotVisOnly val="1"/>
+    <dispBlanksAs val="gap"/>
+  </chart>
+</chartSpace>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>5</col>
+      <colOff>0</colOff>
+      <row>1</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="5400000" cy="2700000"/>
+    <graphicFrame>
+      <nvGraphicFramePr>
+        <cNvPr id="1" name="Chart 1"/>
+        <cNvGraphicFramePr/>
+      </nvGraphicFramePr>
+      <xfrm/>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </graphicFrame>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -424,59 +558,111 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C3"/>
+  <dimension ref="A1:C7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Meno</t>
-        </is>
-      </c>
-      <c r="B1" s="2" t="inlineStr">
-        <is>
-          <t>Vek</t>
+          <t>first_name</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>last_name</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>salary</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>Jana</t>
-        </is>
-      </c>
-      <c r="B2" t="n">
-        <v>30</v>
-      </c>
-      <c r="C2">
-        <f>SUM(B2:B3)</f>
-        <v/>
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>John</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>Doe</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="n">
+        <v>50000</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>Boris</t>
-        </is>
-      </c>
-      <c r="B3" t="n">
-        <v>25</v>
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>Jane</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>Smith</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="n">
+        <v>60000</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>Bob</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>Johnson</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="n">
+        <v>55000</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>Alice</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>Williams</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="n">
+        <v>70000</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>Charlie</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>Brown</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="n">
+        <v>250000</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="n"/>
+      <c r="B7" s="2" t="n"/>
+      <c r="C7" s="2">
+        <f>AVERAGE(C2:C6)</f>
+        <v/>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:A1"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData/>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
 </file>